--- a/Result/checksun_type/電控元件.xlsx
+++ b/Result/checksun_type/電控元件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>100.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>99.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>99.68</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99.68000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>64031.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>25053.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>25053.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>20848.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25588.72</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25588.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>3744.365424784759</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>64031</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>64031.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.88000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>99.73</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>99.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>36812.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14985.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>14985.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15586.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>32703.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>32703.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>306.0413023357032</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>36812</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36812.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.24000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>8495.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12066.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12066.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>15506.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>38344.86</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>38344.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1700.45891910351</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>8495</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8495.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.08000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>99.54</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>100.03</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>100.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8226.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>14445.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>14445</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17200.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>39987.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>39987.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1472.192845477262</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8226</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8226.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>98.22</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.53</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>100.19</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>100.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7703.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>14823.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>14823.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>17899.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>42324.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>42324.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1064.698710101293</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7703</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7703.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>98.47999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>99.51</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>100.38</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>100.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>13691.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>16643.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>16643</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>18149.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>44241.26</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>44241.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-388.5035627748621</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>13691</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13691.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>99.02</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>100.51</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100.51</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22217.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16186.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>16186.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>18551.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>44965.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>44965.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-50.20679649514568</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22217</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22217.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>99.22</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>100.61</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>100.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>20388.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18946.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18946.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>17549.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>46684.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>46684.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-478.6326019350054</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>20388</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>20388.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>99.19999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>99.39</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>100.71</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>100.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>10119.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>19956.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>19956.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>16534.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>47432.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>47432.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-877.6111596371302</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>10119</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>10119.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>99.34</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>100.76</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>100.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>16800.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20976.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>20976</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>17568.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>49534.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>49534.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-315.9872720816966</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>16800</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>16800.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>99.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>100.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11409.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>19656.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>19656.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>16650.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>53289.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>53289.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-218.2036015710146</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11409</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11409.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>83.74</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>86.54</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>97.13</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>97.13</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>16042.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6606.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6606.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>6624.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>9140.06</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>9140.059999999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>421.6277783532978</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>16042</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>16042.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>82.36</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>86.72</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>97.53</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>97.53</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4567.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3893.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>3893.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>5133.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>9947.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>9947.139999999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-453.3445505219588</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4567</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4567.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>82.25999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>87.12</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>98.17</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>98.17</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3580.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>6245.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>6245.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>5101.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>10539.04</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>10539.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-457.6498578251112</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3580</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3580.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>82.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>98.83</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>98.83</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>5670.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>6994.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>6994.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>5683.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>11078.74</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>11078.74</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-341.7056590501461</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>5670</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>5670.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>82.88</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>88.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>99.58</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>99.58</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3174.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>6263.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>6263</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>5784.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>12176.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>12176.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-387.7958872626914</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3174</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3174.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>83.74</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>89.41</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>100.38</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>100.38</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2478.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>6643.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>6643</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>5600.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>12731.18</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>12731.18</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-172.3606458783743</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2478</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2478.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>84.43999999999998</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>90.26</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>101.14</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>101.14</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>16327.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>6372.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>6372.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>6092.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>16739.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>16739.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>216.131150594877</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>16327</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>16327.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>84.88000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>90.96</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>101.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>90.95999999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>101.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>7324.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3956.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3956.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>5269.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>18262.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>18262.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-720.4209669645797</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>7324</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>7324.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>85.38</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>91.74</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>102.57</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>102.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>2012.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4373.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>4373.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>5012.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>18926.78</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>18926.78</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1068.016100372212</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>2012</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2012.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>86.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>92.48</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>103.23</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>92.48</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>103.23</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5074.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>5305.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>5305.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>5080.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>20233.52</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>20233.52</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-957.2942873698221</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5074</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5074.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>87.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>93.04</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>104.01</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>104.01</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1127.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>4557.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>4557</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>4955.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>21365.82</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>21365.82</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1093.002615674628</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1127</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1127.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>23.81</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>23.87</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>23.18</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>39444.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>62992.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>62992.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>45486.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>43879.04</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>43879.04</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3975.805367332854</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>39444</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>39444.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>23.44</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>23.17</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>23.17</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>62964.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>57517.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>57517.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>48308.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>43826.16</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>43826.16</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3029.643795471588</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>62964</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>62964.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>23.04</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>23.18</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>23.18</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>73834.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>47460.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>47460.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>44962.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>43147.02</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>43147.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4089.782842974368</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>73834</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>73834.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>22.96</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23.2</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>40160.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>35455.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>35455.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>41249.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>42160.92</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>42160.92</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-6622.846380729257</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>40160</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>40160.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>23.04</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>98561.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>31684.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>31684.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>40115.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>41699.24</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>41699.24</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-6397.049778210188</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>98561</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>98561.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>23.1</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23.27</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>12070.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>27980.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>27980.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>37110.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>40198.12</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>40198.12</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-12103.26713967544</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>12070</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>12070.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>23.67</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>23.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23.33</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>12677.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>39099.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>39099.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>43688.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>40734.76</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>40734.76</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-10555.8538296374</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>12677</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>12677.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>23.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>23.35</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>13808.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>42463.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>42463.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>91728.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>40962.7</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>40962.7</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-8033.3043213817</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>13808</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>13808.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>23.66</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.43</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.43</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>21306.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>47043.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>47043.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>129167.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>41172.92</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>41172.92</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-4263.937012395647</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>21306</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>21306.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>23.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.47</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>80040.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>48545.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>48545.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>135852.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>41482.14</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>41482.14</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>469.7997508842818</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>80040</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>80040.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>23.97</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>23.08</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.51</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>67665.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>46240.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>46240.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>130923.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>40698.64</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>40698.64</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>922.5737073240161</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>67665</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>67665.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>49.6</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>50.81</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>52.38</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>52.38</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>399.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-18.18075394159126</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>399</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>399.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>49.6</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>50.94</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>52.49</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>52.49</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-15.0438635940464</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>49</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>49.46999999999999</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>51.12</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>52.63</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>52.63</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>0</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>0</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>49.47</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>52.73</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>52.73</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>0</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>49.52999999999999</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>52.83</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>52.83</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>0</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>49.77</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>51.64</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>52.94</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>954.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>832.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>832.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>599.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>96.41047967588315</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>954</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>954.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>51.85</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>53.03</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>53.03</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>302.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>827.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>827.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>79.69718450726532</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>302</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>302.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>51.1</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>52.14</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>53.15</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>53.15</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>422.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>866.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>866.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>122.8318633911232</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>422</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>422.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>51.46</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>52.26</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>53.21</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>53.21</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2176.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>796.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>796.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>167.2088381040944</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2176</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2176.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>51.77999999999999</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>52.44</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>53.28</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>53.28</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>309.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>375.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>375.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>36.70420061890684</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>309</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>51.92</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>52.62</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>53.34</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>53.34</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>928.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>365.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>365.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>48.99385418939238</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>928</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>928.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>40.95</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>42.64</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>43.8</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>43.8</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2421847.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>3791179.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>3791179.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>8441913.0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>18144900.44</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>18144900.44</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-2601451.757577688</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2421847</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2421847.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>40.81</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>42.74</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>43.82</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>43.82</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>4728331.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>4640603.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>4640603.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>10531808.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>18981238.56</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>18981238.56</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2490410.871163477</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>4728331</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>4728331.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>40.88</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>42.91</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>43.9</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>3412251.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>5288830.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>5288830.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>13621042.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>19455359.98</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>19455359.98</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-2489961.07374448</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>3412251</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>3412251.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>41.26000000000001</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>43.17</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>43.99</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>43.99</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>6222251.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>6831106.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>6831106.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>14290454.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>20206651.98</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>20206651.98</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-2259382.753369324</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>6222251</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>6222251.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>41.88</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>44.09</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>44.09</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2171218.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>7709357.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>7709357.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>15585941.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>21466838.98</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>21466838.98</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-2150364.340213053</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2171218</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2171218.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>42.45</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>43.61</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>44.18</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>44.18</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>6668966.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>13092646.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>13092646.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>16658270.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>22433638.84</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>22433638.84</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-1483785.773553628</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>6668966</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>6668966.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>43.84</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>44.26</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>7969466.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>16423013.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>16423013.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>16879569.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>23757455.1</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>23757455.1</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-960439.9006989673</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>7969466</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>7969466.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>44.45</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>44.39</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>44.39</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>11123632.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>21953254.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>21953254.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>16943505.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>24891638.16</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>24891638.16</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-317840.8001673408</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>11123632</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>11123632.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>44.9</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>44.11</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>44.48</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>44.48</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>10613505.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>21749802.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>21749802.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>16553691.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>29980160.82</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>29980160.82</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>273563.01488382</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>10613505</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>10613505.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>45.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>44.63</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>44.63</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>29087663.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>23462526.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>23462526.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>16209059.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>40577803.06</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>40577803.06</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>1163311.96442534</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>29087663</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>29087663.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>44.79</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>44.36</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>44.73</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>44.73</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>23320800.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>20223895.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>20223895.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>14247583.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>46935147.28</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>46935147.28</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>413460.9650408886</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>23320800</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>23320800.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>113.6</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>120.92</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>119.78</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>120.92</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>119.78</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>29791.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>22982.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>22982.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>40802.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>44335.7</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>44335.7</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-13035.51570624486</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>29791</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>29791.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>113.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>120.98</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>119.85</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>120.98</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>119.85</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>19510.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>23117.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>23117</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>46515.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>44284.28</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>44284.28</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-13463.10367456828</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>19510</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>19510.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>113.6</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>121.02</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>119.99</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>121.02</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>119.99</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>18239.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>26262.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>26262.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>58712.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>44406.32</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>44406.32</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-12491.58278379572</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>18239</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>18239.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>114.8</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>121.48</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>120.2</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>120.2</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>28224.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>31335.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>31335.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>109418.7</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>45293.02</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>45293.02</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-10521.38926898507</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>28224</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>28224.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>117.2</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>121.98</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>120.56</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>121.98</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>120.56</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>19148.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>37920.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>37920.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>117145.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>45280.8</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>45280.8</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-8400.88463107754</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>19148</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>19148.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>119.4</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>120.85</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>120.85</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>30464.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>58621.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>58621.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>143616.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>45520.5</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>45520.5</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-4099.132125814023</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>30464</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>30464.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>123.4</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>122.5</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>121.13</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>121.13</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>35237.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>69913.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>69913.39999999999</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>149667.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>46499.54</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>46499.54</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>980.1976004843746</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>35237</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>35237.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>122.55</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>121.53</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>122.55</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>121.53</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>43605.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>91161.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>91161.60000000001</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>147494.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>46060.34</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>46060.34</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>7689.983009464791</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>43605</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>43605.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>131.1</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>122.58</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>121.88</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>122.58</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>121.88</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>61150.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>187501.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>187501.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>144535.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>45866.3</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>45866.3</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>16104.17705767021</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>61150</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>61150.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>132.4</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>122.45</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>122.45</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>122.25</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>122652.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>196369.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>196369.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>140899.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>45827.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>45827.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>25669.48366018973</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>122652</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>122652.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>134.1</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>122.1</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>122.64</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>122.64</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>86923.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>228610.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>228610.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>129751.0</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>46971.36</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>46971.36</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>31827.94010449653</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>86923</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>86923.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>40.14</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>40.34</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>40.88</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>40.88</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1008.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>0</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>0</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>58.77026642390729</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1008</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1008.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>40.35</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>0</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>0</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-2.954113860118895</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>159</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>40.21</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>40.99</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>40.99</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>0</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>0</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>0</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>40.18</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>40.44</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>145.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>208.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>208.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>198.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>0</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>1.17967744797707</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>145</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>40.08</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>40.48</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>41.04</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>195.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>215.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>215.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>192.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>0</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>7.197985201104501</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>195</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>195.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>39.76</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>40.42</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>41.02</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>41.02</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>508.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>176.8</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>176.8</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>197.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>0</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>10.18135394838995</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>508</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>508.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>39.71</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>40.43</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>156.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>118.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>118.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>162.8</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>0</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-19.4560247679305</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>156</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>39.91</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>40.52</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>41.1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>164</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>0</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-23.38599347810501</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>40</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>40.61</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>41.14</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>41.14</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>178.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>188.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>188.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>0</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-15.73644901127915</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>178</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>40.60000000000001</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>40.73</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>41.18</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>41.18</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>169.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>169.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>0</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-19.03222659398224</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>40.68000000000001</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>40.82</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>41.19</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>41.19</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>217.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>217.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>217.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>0</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-4.203615048058737</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>217</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>3847834.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1895258.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1895258.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1471399.6</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2167598.64</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2167598.64</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>128725.1200794668</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>3847834</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>3847834.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>20.13</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>20.13</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>1233198.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1369663.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1369663.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1363475.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2148522.86</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2148522.86</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-64816.37283714046</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>1233198</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>1233198.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1932137.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1292743.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1292743</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1286115.6</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2147117.6</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2147117.6</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-58849.77797382418</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1932137</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1932137.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>19.92</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1146463.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1259223.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1259223.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>1347515.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2123313.92</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2123313.92</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-123110.6146700217</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1146463</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1146463.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>19.51</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>1316660.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1103917.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1103917</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1374269.5</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2138601.12</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2138601.12</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-126335.6451406602</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>1316660</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>1316660.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>19.62</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>1219860.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1047540.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1047540.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1310455.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2150367.64</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2150367.64</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-144666.2370579774</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>1219860</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>1219860.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>19.78</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>20.04</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>848595.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1357286.8</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1357286.8</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1330086.2</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2135168.2</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2135168.2</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-155314.7170449309</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>848595</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>848595.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>19.85</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>20.08</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>20.16</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>20.16</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>1764538.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1279488.2</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1279488.2</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1676457.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2144303.58</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2144303.58</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-125201.4842746884</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>1764538</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>1764538.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>20.09</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>20.15</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>20.15</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>369932.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1435808.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1435808.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>1636380.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2147606.34</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2147606.34</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-175847.8487359602</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>369932</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>369932.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>1034779.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1644622.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1644622</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>1680797.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2162187.9</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2162187.9</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-92497.44622577867</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>1034779</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>1034779.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>20.14</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>20.14</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>2768590.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1573370.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1573370.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>1650880.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2155087.0</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2155087</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-41355.5695603129</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>2768590</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>2768590.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39239,11 +38711,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>2459</t>
@@ -39425,41 +38893,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT90" t="inlineStr">
         <is>
           <t>0</t>
@@ -39480,20 +38944,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>0</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>0</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>0</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>10702402903</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>9579043601</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>16911194399</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>15812987742</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>15882778006</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>10973548400</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>12353712685</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>10709769939</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>18182742782</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>10733728288</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>13958553198</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>71.4</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>73.44</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>76.97</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>76.97</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>15008596.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>11754371.0</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>11754371</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>15914519.0</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>25010878.2</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>25010878.2</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>-2160498.892445303</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>15008596</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>15008596.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>70.72</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>73.54</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>77.12</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>77.12</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>13075405.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>11608166.4</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>11608166.4</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>15786506.8</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>27120049.06</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>27120049.06</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>-2485748.798434014</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>13075405</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>13075405.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>70.42</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>73.75</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>77.39</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>77.39</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>5301284.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>12494332.2</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>12494332.2</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>19370668.8</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>28192896.92</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>28192896.92</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>-2654487.171330955</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>5301284</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>5301284.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>71.02000000000001</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>74.11</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>77.68</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>74.11</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>77.68000000000001</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>16007366.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>15062494.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>15062494</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>20868599.6</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>30624811.72</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>30624811.72</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-1967797.340779051</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>16007366</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>16007366.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>71.62</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>77.95</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>77.95</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>9379204.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>17285360.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>17285360.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>20373527.4</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>31038547.1</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>31038547.1</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>-2063613.606391367</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>9379204</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>9379204.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>72.22</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>74.91</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>78.2</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>14277573.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>20074667.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>20074667</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>20959888.4</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>31462692.26</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>31462692.26</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-1416633.285609268</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>14277573</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>14277573.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>73.22</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>78.45</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>75.31</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>78.45</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>17506234.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>19964847.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>19964847.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>21501629.5</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>32073496.64</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>32073496.64</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>-966606.8885773644</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>17506234</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>17506234.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>74.26</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>75.66</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>78.72</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>78.72</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>18142093.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>26247005.4</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>26247005.4</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>22381926.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>32414899.56</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>32414899.56</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-635118.3253683113</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>18142093</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>18142093.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>74.44</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>75.88</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>78.93</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>78.93000000000001</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>27121698.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>26674705.2</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>26674705.2</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>23833894.1</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>33359607.38</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>33359607.38</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>-207008.1877350844</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>27121698</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>27121698.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>74.67999999999999</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>76.16</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>79.16</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>79.16</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>23325737.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>23461694.4</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>23461694.4</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>23010323.4</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>34773636.02</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>34773636.02</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>-550129.6629827917</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>23325737</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>23325737.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>74.8</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>76.33</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>79.42</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>79.42</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>13728474.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>21845109.8</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>21845109.8</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>22848112.3</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>36198094.2</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>36198094.2</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>-613945.6039444208</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>13728474</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>13728474.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48783,11 @@
           <t>31.49</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>32.14</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48834,16 @@
           <t>3040182.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>2456523.0</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>2456523</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>3732357.5</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>7654335.3</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>7654335.3</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48860,10 @@
           <t>-2510959.699003746</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>3040182</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>3040182.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49029,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49213,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>32.57</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>32.17</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49264,16 @@
           <t>2456462.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>2783562.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>2783562</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>3920197.9</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>7978127.08</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>7978127.08</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49290,10 @@
           <t>-2647451.513904463</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>2456462</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>2456462.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49459,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49643,11 @@
           <t>31.35</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>32.22</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>32.22</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49694,16 @@
           <t>2462064.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>2895590.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>2895590.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>4503246.3</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>8193565.74</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>8193565.74</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49720,10 @@
           <t>-2685346.552551758</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>2462064</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>2462064.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50073,11 @@
           <t>31.67000000000001</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>32.27</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>32.27</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50124,16 @@
           <t>2854768.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>3012758.2</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>3012758.2</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>5947125.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>8925246.32</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>8925246.32</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50150,10 @@
           <t>-2644177.302313902</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>2854768</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>2854768.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50319,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50503,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>32.29</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>32.29</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50554,16 @@
           <t>1469139.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>3883096.4</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>3883096.4</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>8394042.6</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>9103186.62</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>9103186.619999999</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50580,10 @@
           <t>-2533004.612605754</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>1469139</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>1469139.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50749,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50933,11 @@
           <t>32.4</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>32.32</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>32.32</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50984,16 @@
           <t>4675377.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>5008192.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>5008192</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>20061078.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>9851668.88</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>9851668.880000001</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51010,10 @@
           <t>-2135261.784001052</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>4675377</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>4675377.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51179,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51363,11 @@
           <t>32.86</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>32.47</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>32.31</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>32.31</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51414,16 @@
           <t>3016605.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>5056833.8</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>5056833.8</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>22899336.4</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>9883789.8</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>9883789.800000001</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51440,10 @@
           <t>-1834323.893708583</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>3016605</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>3016605.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51793,11 @@
           <t>33.12</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>32.44</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>32.28</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51844,16 @@
           <t>3047902.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>6110902.0</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>6110902</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>25118237.3</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>9871501.58</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>9871501.58</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51870,10 @@
           <t>-1161175.482801178</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>3047902</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>3047902.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52039,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52223,11 @@
           <t>33.22</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>32.22</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>32.22</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52274,16 @@
           <t>7206459.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>8881492.2</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>8881492.199999999</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>27788001.9</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>9888488.0</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>9888488</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52300,10 @@
           <t>-161417.5928334147</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>7206459</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>7206459.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52469,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52653,11 @@
           <t>33.97000000000001</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>32.28</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52704,16 @@
           <t>7094617.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>12904988.8</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>12904988.8</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>27334017.0</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>9783605.2</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>9783605.199999999</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52730,10 @@
           <t>827013.1997217275</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>7094617</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>7094617.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52899,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53083,11 @@
           <t>34.73999999999999</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>32.09</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>32.09</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53134,16 @@
           <t>4918586.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>35113964.8</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>35113964.8</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>26772613.7</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>9660599.88</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>9660599.880000001</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53160,10 @@
           <t>2221504.074810442</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>4918586</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>4918586.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53329,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53513,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53564,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53590,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>2683545818</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53759,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53943,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53994,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54020,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>4682266073</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54189,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54373,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54424,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54450,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>11515775721</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54619,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54803,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54854,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54880,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>3032171594</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55049,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55233,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55284,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55310,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>3089667541</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55479,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55663,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55714,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55740,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>2778009293</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55909,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56093,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56144,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56170,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>3068959808</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56339,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56523,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56574,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56600,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>3989400881</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56769,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56953,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57004,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57030,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>7366534520</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57199,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57383,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57434,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57460,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>5064644998</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
@@ -58425,7 +57629,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -58609,15 +57813,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM134" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -58664,20 +57864,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX134" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ134" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ134" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
@@ -58694,8 +57890,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD134" t="n">
-        <v>1385646995</v>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
@@ -58861,7 +58059,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -59045,15 +58243,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM135" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -59100,20 +58294,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX135" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ135" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
@@ -59130,8 +58320,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD135" t="n">
-        <v>3512622548</v>
+      <c r="BD135" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
@@ -59297,7 +58489,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -59481,15 +58673,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM136" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -59536,20 +58724,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX136" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ136" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ136" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
@@ -59566,8 +58750,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD136" t="n">
-        <v>6744255965</v>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
@@ -59733,7 +58919,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -59917,15 +59103,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM137" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -59972,20 +59154,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX137" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ137" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ137" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
@@ -60002,8 +59180,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD137" t="n">
-        <v>4850127005</v>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
@@ -60169,7 +59349,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -60353,15 +59533,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM138" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -60408,20 +59584,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX138" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ138" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ138" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
@@ -60438,8 +59610,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD138" t="n">
-        <v>4661687858</v>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
@@ -60605,7 +59779,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -60789,15 +59963,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM139" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -60844,20 +60014,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX139" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ139" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ139" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
@@ -60874,8 +60040,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD139" t="n">
-        <v>10708653199</v>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
@@ -61041,7 +60209,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -61225,15 +60393,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM140" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -61280,20 +60444,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX140" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ140" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
@@ -61310,8 +60470,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD140" t="n">
-        <v>7717712495</v>
+      <c r="BD140" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE140" t="inlineStr">
         <is>
@@ -61477,7 +60639,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -61661,15 +60823,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM141" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -61716,20 +60874,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX141" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ141" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
@@ -61746,8 +60900,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD141" t="n">
-        <v>13894804772</v>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
@@ -61913,7 +61069,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -62097,15 +61253,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM142" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -62152,20 +61304,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX142" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ142" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
@@ -62182,8 +61330,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD142" t="n">
-        <v>12606646015</v>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
@@ -62349,7 +61499,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -62533,15 +61683,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM143" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -62588,20 +61734,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX143" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ143" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ143" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
@@ -62618,8 +61760,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD143" t="n">
-        <v>12847401961</v>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
@@ -62785,7 +61929,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -62969,15 +62113,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM144" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -63024,20 +62164,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX144" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ144" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
@@ -63054,8 +62190,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD144" t="n">
-        <v>17904603214</v>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
@@ -63221,7 +62359,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -63405,15 +62543,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM145" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -63460,20 +62594,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX145" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX145" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ145" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ145" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
@@ -63490,8 +62620,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD145" t="n">
-        <v>8385497650</v>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
